--- a/data/German_Interview_Nouns_Vocabulary - Copy.xlsx
+++ b/data/German_Interview_Nouns_Vocabulary - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deutsch\german-flashcards-architecture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B378381-1668-41A9-B5C9-E769B07CB6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A5F78D-11C1-4740-9487-64B16145E4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="15600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adjectives_Master" sheetId="1" r:id="rId1"/>
@@ -2288,7 +2288,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2320,6 +2320,13 @@
       <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2346,7 +2353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2360,29 +2367,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2473,6 +2465,24 @@
       </font>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2487,14 +2497,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AdjectivesTable" displayName="AdjectivesTable" ref="A1:E151" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AdjectivesTable" displayName="AdjectivesTable" ref="A1:E151" dataDxfId="5">
   <autoFilter ref="A1:E151" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="German adjective" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Meaning (simple)" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="English word" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="German example sentence" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="English example sentence" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="German adjective" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Meaning (simple)" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="English word" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="German example sentence" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="English example sentence" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4614,7 +4624,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="5" t="s">
         <v>534</v>
       </c>
       <c r="B108" s="4" t="s">
